--- a/Sep_2026/Daily Sale/29-09-26/Salman.xlsx
+++ b/Sep_2026/Daily Sale/29-09-26/Salman.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0DA798-A8DF-4886-8D06-BEE1AEA6CDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41FA1AC3-1C4C-46D0-A7F7-45E39445F001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7585,20 +7585,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>4</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L16" s="118">
         <f>$I16*U16</f>
@@ -7606,19 +7604,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P16" s="118">
         <f>M16+N16+O16</f>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="318"/>
       <c r="S16" s="269">
@@ -7662,19 +7660,19 @@
       </c>
       <c r="G17" s="287"/>
       <c r="H17" s="96">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>209.85</v>
+        <v>1049.25</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>16.788</v>
+        <v>83.94</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
-        <v>7.3447500000000003</v>
+        <v>36.723750000000003</v>
       </c>
       <c r="L17" s="119">
         <f>$I17*U17</f>
@@ -7682,19 +7680,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>185.71724999999998</v>
+        <v>928.58625000000006</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>39.661016949152526</v>
+        <v>198.30508474576263</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>1.1268913347457625</v>
+        <v>5.6344566737288133</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>226.50515828389825</v>
+        <v>1132.5257914194915</v>
       </c>
       <c r="Q17" s="319"/>
       <c r="S17" s="269">
@@ -7739,20 +7737,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>2</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>104.925</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>8.3940000000000001</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>3.6723750000000002</v>
+        <v>0</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -7760,19 +7756,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>92.858624999999989</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>19.830508474576263</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>0.56344566737288126</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="5"/>
-        <v>113.25257914194913</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="319"/>
       <c r="S18" s="269">
@@ -8252,19 +8248,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>524.625</v>
+        <v>1049.25</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>41.97</v>
+        <v>83.94</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>18.361875000000001</v>
+        <v>36.723750000000003</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -8272,19 +8268,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>464.29312499999992</v>
+        <v>928.58625000000006</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>99.152542372881314</v>
+        <v>198.30508474576263</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>2.8172283368644062</v>
+        <v>5.6344566737288133</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>566.26289570974564</v>
+        <v>1132.5257914194915</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -8338,7 +8334,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>524.625</v>
+        <v>1049.25</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8359,7 +8355,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>41.97</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8380,7 +8376,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>18.361875000000001</v>
+        <v>36.723750000000003</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8402,7 +8398,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>464.29312499999997</v>
+        <v>928.58624999999995</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8426,7 +8422,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>99.152542372881314</v>
+        <v>198.30508474576263</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8448,7 +8444,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>563.4456673728813</v>
+        <v>1126.8913347457626</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8473,7 +8469,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>2.8172283368644067</v>
+        <v>5.6344566737288133</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8483,7 +8479,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>566.26289570974575</v>
+        <v>1132.5257914194915</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -9089,18 +9085,20 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96"/>
+      <c r="H17" s="96">
+        <v>20</v>
+      </c>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>0</v>
+        <v>1049.25</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>0</v>
+        <v>83.94</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
-        <v>0</v>
+        <v>36.723750000000003</v>
       </c>
       <c r="L17" s="119">
         <f>$I17*U17</f>
@@ -9108,19 +9106,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>0</v>
+        <v>928.58625000000006</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>0</v>
+        <v>198.30508474576263</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>0</v>
+        <v>5.6344566737288133</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>0</v>
+        <v>1132.5257914194915</v>
       </c>
       <c r="Q17" s="319"/>
       <c r="S17" s="269">
@@ -9238,20 +9236,18 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>4</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -9259,19 +9255,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="319"/>
       <c r="S19" s="269">
@@ -9312,20 +9308,18 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>2</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>145.28</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>11.622400000000001</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>5.0848000000000004</v>
+        <v>0</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -9333,24 +9327,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>128.5728</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>27.457627118644069</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>0.78015213559322039</v>
+        <v>0</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="5"/>
-        <v>156.8105792542373</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="319"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>7.4671704406779664</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -9391,20 +9385,18 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>4</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -9412,19 +9404,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="319"/>
       <c r="S21" s="269">
@@ -9682,19 +9674,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>726.40000000000009</v>
+        <v>1049.25</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>58.112000000000009</v>
+        <v>83.94</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>25.423999999999999</v>
+        <v>36.723750000000003</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -9702,19 +9694,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>642.86400000000003</v>
+        <v>928.58625000000006</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>137.28813559322035</v>
+        <v>198.30508474576263</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>3.9007606779661019</v>
+        <v>5.6344566737288133</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>784.05289627118646</v>
+        <v>1132.5257914194915</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -9768,7 +9760,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>726.40000000000009</v>
+        <v>1049.25</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9789,7 +9781,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>58.112000000000009</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9810,7 +9802,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>25.423999999999999</v>
+        <v>36.723750000000003</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9832,7 +9824,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>642.86400000000015</v>
+        <v>928.58624999999995</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9856,7 +9848,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>137.28813559322035</v>
+        <v>198.30508474576263</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9878,7 +9870,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>780.15213559322046</v>
+        <v>1126.8913347457626</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -9903,7 +9895,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>3.9007606779661024</v>
+        <v>5.6344566737288133</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -9913,7 +9905,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>784.05289627118657</v>
+        <v>1132.5257914194915</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10446,19 +10438,19 @@
       </c>
       <c r="G16" s="286"/>
       <c r="H16" s="112">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>104.925</v>
+        <v>1049.25</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>8.3940000000000001</v>
+        <v>83.94</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
-        <v>3.6723750000000002</v>
+        <v>36.723750000000003</v>
       </c>
       <c r="L16" s="118">
         <f>$I16*U16</f>
@@ -10466,19 +10458,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>92.858624999999989</v>
+        <v>928.58625000000006</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>19.830508474576263</v>
+        <v>198.30508474576263</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>0.56344566737288126</v>
+        <v>5.6344566737288133</v>
       </c>
       <c r="P16" s="118">
         <f>M16+N16+O16</f>
-        <v>113.25257914194913</v>
+        <v>1132.5257914194915</v>
       </c>
       <c r="Q16" s="318"/>
       <c r="S16" s="269">
@@ -10521,20 +10513,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>4</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L17" s="119">
         <f>$I17*U17</f>
@@ -10542,19 +10532,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="319"/>
       <c r="S17" s="269">
@@ -10599,20 +10589,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>4</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -10620,19 +10608,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="5"/>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="319"/>
       <c r="S18" s="269">
@@ -11112,19 +11100,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>524.625</v>
+        <v>1049.25</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>41.97</v>
+        <v>83.94</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>18.361875000000001</v>
+        <v>36.723750000000003</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -11132,19 +11120,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>464.29312499999997</v>
+        <v>928.58625000000006</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>99.152542372881314</v>
+        <v>198.30508474576263</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>2.8172283368644067</v>
+        <v>5.6344566737288133</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>566.26289570974564</v>
+        <v>1132.5257914194915</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -11198,7 +11186,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>524.625</v>
+        <v>1049.25</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11219,7 +11207,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>41.97</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11240,7 +11228,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>18.361875000000001</v>
+        <v>36.723750000000003</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11262,7 +11250,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>464.29312499999997</v>
+        <v>928.58624999999995</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11286,7 +11274,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>99.152542372881314</v>
+        <v>198.30508474576263</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11308,7 +11296,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>563.4456673728813</v>
+        <v>1126.8913347457626</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -11333,7 +11321,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>2.8172283368644067</v>
+        <v>5.6344566737288133</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -11343,7 +11331,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>566.26289570974575</v>
+        <v>1132.5257914194915</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -11875,18 +11863,20 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112"/>
+      <c r="H16" s="112">
+        <v>20</v>
+      </c>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>0</v>
+        <v>1049.25</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>0</v>
+        <v>83.94</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
-        <v>0</v>
+        <v>36.723750000000003</v>
       </c>
       <c r="L16" s="118">
         <f>$I16*U16</f>
@@ -11894,19 +11884,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>0</v>
+        <v>928.58625000000006</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>0</v>
+        <v>198.30508474576263</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>0</v>
+        <v>5.6344566737288133</v>
       </c>
       <c r="P16" s="118">
         <f>M16+N16+O16</f>
-        <v>0</v>
+        <v>1132.5257914194915</v>
       </c>
       <c r="Q16" s="318"/>
       <c r="S16" s="269">
@@ -12098,20 +12088,18 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>4</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -12119,19 +12107,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="319"/>
       <c r="S19" s="269">
@@ -12172,20 +12160,18 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>2</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>145.28</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>11.622400000000001</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>5.0848000000000004</v>
+        <v>0</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -12193,24 +12179,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>128.5728</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>27.457627118644069</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>0.78015213559322039</v>
+        <v>0</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="5"/>
-        <v>156.8105792542373</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="319"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>7.4671704406779664</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -12251,20 +12237,18 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>4</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -12272,19 +12256,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="319"/>
       <c r="S21" s="269">
@@ -12542,19 +12526,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>726.40000000000009</v>
+        <v>1049.25</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>58.112000000000009</v>
+        <v>83.94</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>25.423999999999999</v>
+        <v>36.723750000000003</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -12562,19 +12546,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>642.86400000000003</v>
+        <v>928.58625000000006</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>137.28813559322035</v>
+        <v>198.30508474576263</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>3.9007606779661019</v>
+        <v>5.6344566737288133</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>784.05289627118646</v>
+        <v>1132.5257914194915</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -12628,7 +12612,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>726.40000000000009</v>
+        <v>1049.25</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12649,7 +12633,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>58.112000000000009</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12670,7 +12654,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>25.423999999999999</v>
+        <v>36.723750000000003</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12692,7 +12676,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>642.86400000000015</v>
+        <v>928.58624999999995</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12716,7 +12700,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>137.28813559322035</v>
+        <v>198.30508474576263</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12738,7 +12722,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>780.15213559322046</v>
+        <v>1126.8913347457626</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -12763,7 +12747,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>3.9007606779661024</v>
+        <v>5.6344566737288133</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -12773,7 +12757,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>784.05289627118657</v>
+        <v>1132.5257914194915</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -13305,20 +13289,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>4</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L16" s="118">
         <f>$I16*U16</f>
@@ -13326,19 +13308,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P16" s="118">
         <f>M16+N16+O16</f>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="318"/>
       <c r="S16" s="269">
@@ -13381,20 +13363,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>4</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L17" s="119">
         <f>$I17*U17</f>
@@ -13402,19 +13382,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="319"/>
       <c r="S17" s="269">
@@ -13459,20 +13439,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>2</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>104.925</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>8.3940000000000001</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>3.6723750000000002</v>
+        <v>0</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -13480,19 +13458,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>92.858624999999989</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>19.830508474576263</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>0.56344566737288126</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="5"/>
-        <v>113.25257914194913</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="319"/>
       <c r="S18" s="269">
@@ -13683,18 +13661,20 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96"/>
+      <c r="H21" s="96">
+        <v>20</v>
+      </c>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1452.8</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>116.224</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -13702,19 +13682,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.8015213559322039</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1568.1057925423729</v>
       </c>
       <c r="Q21" s="319"/>
       <c r="S21" s="269">
@@ -13972,19 +13952,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>524.625</v>
+        <v>1452.8</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>41.97</v>
+        <v>116.224</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>18.361875000000001</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -13992,19 +13972,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>464.29312499999992</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>99.152542372881314</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>2.8172283368644062</v>
+        <v>7.8015213559322039</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>566.26289570974564</v>
+        <v>1568.1057925423729</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -14058,7 +14038,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>524.625</v>
+        <v>1452.8</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -14079,7 +14059,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>41.97</v>
+        <v>116.224</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -14100,7 +14080,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>18.361875000000001</v>
+        <v>50.848000000000006</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -14122,7 +14102,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>464.29312499999997</v>
+        <v>1285.7280000000001</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -14146,7 +14126,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>99.152542372881314</v>
+        <v>274.57627118644069</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -14168,7 +14148,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>563.4456673728813</v>
+        <v>1560.3042711864407</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14193,7 +14173,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>2.8172283368644067</v>
+        <v>7.8015213559322039</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14203,7 +14183,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>566.26289570974575</v>
+        <v>1568.1057925423729</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -14735,20 +14715,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>2</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>104.925</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>8.3940000000000001</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
-        <v>3.6723750000000002</v>
+        <v>0</v>
       </c>
       <c r="L16" s="118">
         <f>$I16*U16</f>
@@ -14756,19 +14734,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>92.858624999999989</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>19.830508474576263</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>0.56344566737288126</v>
+        <v>0</v>
       </c>
       <c r="P16" s="118">
         <f>M16+N16+O16</f>
-        <v>113.25257914194913</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="318"/>
       <c r="S16" s="269">
@@ -14811,20 +14789,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>4</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L17" s="119">
         <f>$I17*U17</f>
@@ -14832,19 +14808,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="319"/>
       <c r="S17" s="269">
@@ -14889,20 +14865,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>4</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -14910,19 +14884,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="5"/>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="319"/>
       <c r="S18" s="269">
@@ -15113,18 +15087,20 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96"/>
+      <c r="H21" s="96">
+        <v>20</v>
+      </c>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1452.8</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>116.224</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -15132,19 +15108,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.8015213559322039</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1568.1057925423729</v>
       </c>
       <c r="Q21" s="319"/>
       <c r="S21" s="269">
@@ -15402,19 +15378,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>524.625</v>
+        <v>1452.8</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>41.97</v>
+        <v>116.224</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>18.361875000000001</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -15422,19 +15398,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>464.29312499999997</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>99.152542372881314</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>2.8172283368644067</v>
+        <v>7.8015213559322039</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>566.26289570974564</v>
+        <v>1568.1057925423729</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -15488,7 +15464,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>524.625</v>
+        <v>1452.8</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -15509,7 +15485,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>41.97</v>
+        <v>116.224</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -15530,7 +15506,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>18.361875000000001</v>
+        <v>50.848000000000006</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -15552,7 +15528,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>464.29312499999997</v>
+        <v>1285.7280000000001</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -15576,7 +15552,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>99.152542372881314</v>
+        <v>274.57627118644069</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -15598,7 +15574,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>563.4456673728813</v>
+        <v>1560.3042711864407</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15623,7 +15599,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>2.8172283368644067</v>
+        <v>7.8015213559322039</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15633,7 +15609,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>566.26289570974575</v>
+        <v>1568.1057925423729</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -16388,20 +16364,18 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>4</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -16409,19 +16383,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="319"/>
       <c r="S19" s="269">
@@ -16463,19 +16437,19 @@
       </c>
       <c r="G20" s="287"/>
       <c r="H20" s="96">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>1452.8</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>116.224</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -16483,24 +16457,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>7.8015213559322039</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>1568.1057925423729</v>
       </c>
       <c r="Q20" s="319"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>14.934340881355933</v>
+        <v>74.671704406779668</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -16541,20 +16515,18 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>2</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>145.28</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>11.622400000000001</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>5.0848000000000004</v>
+        <v>0</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -16562,19 +16534,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>128.5728</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>27.457627118644069</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>0.78015213559322039</v>
+        <v>0</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>156.8105792542373</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="319"/>
       <c r="S21" s="269">
@@ -16832,19 +16804,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>726.4</v>
+        <v>1452.8</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>58.112000000000002</v>
+        <v>116.224</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>25.424000000000003</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -16852,19 +16824,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>642.86400000000003</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>137.28813559322035</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>3.9007606779661019</v>
+        <v>7.8015213559322039</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>784.05289627118646</v>
+        <v>1568.1057925423729</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -16918,7 +16890,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>726.4</v>
+        <v>1452.8</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -16939,7 +16911,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>58.112000000000002</v>
+        <v>116.224</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -16960,7 +16932,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>25.424000000000003</v>
+        <v>50.848000000000006</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -16982,7 +16954,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>642.86400000000003</v>
+        <v>1285.7280000000001</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -17006,7 +16978,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>137.28813559322035</v>
+        <v>274.57627118644069</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -17028,7 +17000,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>780.15213559322035</v>
+        <v>1560.3042711864407</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17053,7 +17025,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>3.9007606779661019</v>
+        <v>7.8015213559322039</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17063,7 +17035,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>784.05289627118646</v>
+        <v>1568.1057925423729</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -17595,20 +17567,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>4</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L16" s="118">
         <f>$I16*U16</f>
@@ -17616,19 +17586,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P16" s="118">
         <f>M16+N16+O16</f>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="318"/>
       <c r="S16" s="269">
@@ -17671,20 +17641,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>2</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>104.925</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>8.3940000000000001</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
-        <v>3.6723750000000002</v>
+        <v>0</v>
       </c>
       <c r="L17" s="119">
         <f>$I17*U17</f>
@@ -17692,19 +17660,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>92.858624999999989</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>19.830508474576263</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>0.56344566737288126</v>
+        <v>0</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>113.25257914194913</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="319"/>
       <c r="S17" s="269">
@@ -17749,20 +17717,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>4</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -17770,19 +17736,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="5"/>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="319"/>
       <c r="S18" s="269">
@@ -17896,18 +17862,20 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96"/>
+      <c r="H20" s="96">
+        <v>20</v>
+      </c>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1452.8</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>116.224</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -17915,24 +17883,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.8015213559322039</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1568.1057925423729</v>
       </c>
       <c r="Q20" s="319"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>0</v>
+        <v>74.671704406779668</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -18262,19 +18230,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>524.625</v>
+        <v>1452.8</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>41.97</v>
+        <v>116.224</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>18.361875000000001</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -18282,19 +18250,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>464.29312499999997</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>99.152542372881314</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>2.8172283368644067</v>
+        <v>7.8015213559322039</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>566.26289570974564</v>
+        <v>1568.1057925423729</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -18348,7 +18316,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>524.625</v>
+        <v>1452.8</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -18369,7 +18337,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>41.97</v>
+        <v>116.224</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -18390,7 +18358,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>18.361875000000001</v>
+        <v>50.848000000000006</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -18412,7 +18380,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>464.29312499999997</v>
+        <v>1285.7280000000001</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -18436,7 +18404,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>99.152542372881314</v>
+        <v>274.57627118644069</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -18458,7 +18426,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>563.4456673728813</v>
+        <v>1560.3042711864407</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18483,7 +18451,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>2.8172283368644067</v>
+        <v>7.8015213559322039</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18493,7 +18461,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>566.26289570974575</v>
+        <v>1568.1057925423729</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -19249,19 +19217,19 @@
       </c>
       <c r="G19" s="287"/>
       <c r="H19" s="96">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>1452.8</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>116.224</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -19269,19 +19237,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>7.8015213559322039</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>1568.1057925423729</v>
       </c>
       <c r="Q19" s="319"/>
       <c r="S19" s="269">
@@ -19322,20 +19290,18 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>4</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -19343,24 +19309,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="319"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>14.934340881355933</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -19401,20 +19367,18 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>2</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>145.28</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>11.622400000000001</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>5.0848000000000004</v>
+        <v>0</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -19422,19 +19386,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>128.5728</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>27.457627118644069</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>0.78015213559322039</v>
+        <v>0</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>156.8105792542373</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="319"/>
       <c r="S21" s="269">
@@ -19692,19 +19656,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>726.4</v>
+        <v>1452.8</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>58.112000000000002</v>
+        <v>116.224</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>25.424000000000003</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -19712,19 +19676,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>642.86400000000003</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>137.28813559322035</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>3.9007606779661019</v>
+        <v>7.8015213559322039</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>784.05289627118646</v>
+        <v>1568.1057925423729</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -19778,7 +19742,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>726.4</v>
+        <v>1452.8</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19799,7 +19763,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>58.112000000000002</v>
+        <v>116.224</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19820,7 +19784,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>25.424000000000003</v>
+        <v>50.848000000000006</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19842,7 +19806,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>642.86400000000003</v>
+        <v>1285.7280000000001</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19866,7 +19830,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>137.28813559322035</v>
+        <v>274.57627118644069</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19888,7 +19852,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>780.15213559322035</v>
+        <v>1560.3042711864407</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -19913,7 +19877,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>3.9007606779661019</v>
+        <v>7.8015213559322039</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -19923,7 +19887,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>784.05289627118646</v>
+        <v>1568.1057925423729</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -20455,20 +20419,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>4</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L16" s="118">
         <f>$I16*U16</f>
@@ -20476,19 +20438,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P16" s="118">
         <f>M16+N16+O16</f>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="318"/>
       <c r="S16" s="269">
@@ -20531,20 +20493,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>2</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>104.925</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>8.3940000000000001</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
-        <v>3.6723750000000002</v>
+        <v>0</v>
       </c>
       <c r="L17" s="119">
         <f>$I17*U17</f>
@@ -20552,19 +20512,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>92.858624999999989</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>19.830508474576263</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>0.56344566737288126</v>
+        <v>0</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>113.25257914194913</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="319"/>
       <c r="S17" s="269">
@@ -20609,20 +20569,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>4</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -20630,19 +20588,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="5"/>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="319"/>
       <c r="S18" s="269">
@@ -20684,18 +20642,20 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96"/>
+      <c r="H19" s="96">
+        <v>20</v>
+      </c>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1452.8</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>116.224</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -20703,19 +20663,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.8015213559322039</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1568.1057925423729</v>
       </c>
       <c r="Q19" s="319"/>
       <c r="S19" s="269">
@@ -21122,19 +21082,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>524.625</v>
+        <v>1452.8</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>41.97</v>
+        <v>116.224</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>18.361875000000001</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -21142,19 +21102,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>464.29312499999997</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>99.152542372881314</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>2.8172283368644067</v>
+        <v>7.8015213559322039</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>566.26289570974564</v>
+        <v>1568.1057925423729</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -21208,7 +21168,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>524.625</v>
+        <v>1452.8</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -21229,7 +21189,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>41.97</v>
+        <v>116.224</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -21250,7 +21210,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>18.361875000000001</v>
+        <v>50.848000000000006</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -21272,7 +21232,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>464.29312499999997</v>
+        <v>1285.7280000000001</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -21296,7 +21256,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>99.152542372881314</v>
+        <v>274.57627118644069</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -21318,7 +21278,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>563.4456673728813</v>
+        <v>1560.3042711864407</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -21343,7 +21303,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>2.8172283368644067</v>
+        <v>7.8015213559322039</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -21353,7 +21313,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>566.26289570974575</v>
+        <v>1568.1057925423729</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24523,20 +24483,18 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>2</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>145.28</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>11.622400000000001</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>5.0848000000000004</v>
+        <v>0</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -24544,19 +24502,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>128.5728</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>27.457627118644069</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>0.78015213559322039</v>
+        <v>0</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="5"/>
-        <v>156.8105792542373</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="319"/>
       <c r="S19" s="269">
@@ -24597,20 +24555,18 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>4</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -24618,24 +24574,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="319"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>14.934340881355933</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -24676,20 +24632,18 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>4</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -24697,19 +24651,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="319"/>
       <c r="S21" s="269">
@@ -24967,19 +24921,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>726.40000000000009</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>58.112000000000009</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>25.423999999999999</v>
+        <v>0</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -24987,19 +24941,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>642.86400000000003</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>137.28813559322035</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>3.9007606779661019</v>
+        <v>0</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>784.05289627118646</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -25053,7 +25007,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>726.40000000000009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25074,7 +25028,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>58.112000000000009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25095,7 +25049,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>25.423999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25117,7 +25071,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>642.86400000000015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25141,7 +25095,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>137.28813559322035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25163,7 +25117,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>780.15213559322046</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25188,7 +25142,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>3.9007606779661024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25198,7 +25152,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>784.05289627118657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25730,20 +25684,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>4</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L16" s="118">
         <f>$I16*U16</f>
@@ -25751,19 +25703,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P16" s="118">
         <f>M16+N16+O16</f>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="318"/>
       <c r="S16" s="269">
@@ -25806,20 +25758,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>4</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L17" s="119">
         <f>$I17*U17</f>
@@ -25827,19 +25777,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="319"/>
       <c r="S17" s="269">
@@ -25884,20 +25834,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>2</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>104.925</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>8.3940000000000001</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>3.6723750000000002</v>
+        <v>0</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -25905,19 +25853,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>92.858624999999989</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>19.830508474576263</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>0.56344566737288126</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="5"/>
-        <v>113.25257914194913</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="319"/>
       <c r="S18" s="269">
@@ -26397,19 +26345,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>524.625</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>41.97</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>18.361875000000001</v>
+        <v>0</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -26417,19 +26365,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>464.29312499999992</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>99.152542372881314</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>2.8172283368644062</v>
+        <v>0</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>566.26289570974564</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -26483,7 +26431,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>524.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26504,7 +26452,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>41.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26525,7 +26473,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>18.361875000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26547,7 +26495,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>464.29312499999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26571,7 +26519,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>99.152542372881314</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26593,7 +26541,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>563.4456673728813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26618,7 +26566,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>2.8172283368644067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26628,7 +26576,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>566.26289570974575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -27383,20 +27331,18 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>2</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>145.28</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>11.622400000000001</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>5.0848000000000004</v>
+        <v>0</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -27404,19 +27350,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>128.5728</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>27.457627118644069</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>0.78015213559322039</v>
+        <v>0</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="5"/>
-        <v>156.8105792542373</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="319"/>
       <c r="S19" s="269">
@@ -27457,20 +27403,18 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>4</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -27478,24 +27422,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="319"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>14.934340881355933</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -27536,20 +27480,18 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>4</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -27557,19 +27499,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="319"/>
       <c r="S21" s="269">
@@ -27827,19 +27769,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>726.40000000000009</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>58.112000000000009</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>25.423999999999999</v>
+        <v>0</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -27847,19 +27789,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>642.86400000000003</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>137.28813559322035</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>3.9007606779661019</v>
+        <v>0</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>784.05289627118646</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -27913,7 +27855,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>726.40000000000009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27934,7 +27876,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>58.112000000000009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27955,7 +27897,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>25.423999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27977,7 +27919,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>642.86400000000015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28001,7 +27943,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>137.28813559322035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28023,7 +27965,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>780.15213559322046</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28048,7 +27990,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>3.9007606779661024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28058,7 +28000,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>784.05289627118657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -28590,20 +28532,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>2</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>104.925</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>8.3940000000000001</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
-        <v>3.6723750000000002</v>
+        <v>0</v>
       </c>
       <c r="L16" s="118">
         <f>$I16*U16</f>
@@ -28611,19 +28551,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>92.858624999999989</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>19.830508474576263</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>0.56344566737288126</v>
+        <v>0</v>
       </c>
       <c r="P16" s="118">
         <f>M16+N16+O16</f>
-        <v>113.25257914194913</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="318"/>
       <c r="S16" s="269">
@@ -28666,20 +28606,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>4</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L17" s="119">
         <f>$I17*U17</f>
@@ -28687,19 +28625,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="319"/>
       <c r="S17" s="269">
@@ -28744,20 +28682,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>4</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -28765,19 +28701,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="5"/>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="319"/>
       <c r="S18" s="269">
@@ -29257,19 +29193,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>524.625</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>41.97</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>18.361875000000001</v>
+        <v>0</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -29277,19 +29213,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>464.29312499999997</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>99.152542372881314</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>2.8172283368644067</v>
+        <v>0</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>566.26289570974564</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -29343,7 +29279,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>524.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29364,7 +29300,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>41.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29385,7 +29321,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>18.361875000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29407,7 +29343,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>464.29312499999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29431,7 +29367,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>99.152542372881314</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29453,7 +29389,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>563.4456673728813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29478,7 +29414,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>2.8172283368644067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29488,7 +29424,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>566.26289570974575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -30243,20 +30179,18 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>4</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -30264,19 +30198,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="319"/>
       <c r="S19" s="269">
@@ -30317,20 +30251,18 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>4</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -30338,24 +30270,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="319"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>14.934340881355933</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -30396,20 +30328,18 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>2</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>145.28</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>11.622400000000001</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>5.0848000000000004</v>
+        <v>0</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -30417,19 +30347,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>128.5728</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>27.457627118644069</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>0.78015213559322039</v>
+        <v>0</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>156.8105792542373</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="319"/>
       <c r="S21" s="269">
@@ -30687,19 +30617,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>726.4</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>58.112000000000002</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>25.424000000000003</v>
+        <v>0</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -30707,19 +30637,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>642.86400000000003</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>137.28813559322035</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>3.9007606779661019</v>
+        <v>0</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>784.05289627118646</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -30773,7 +30703,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>726.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30794,7 +30724,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>58.112000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30815,7 +30745,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>25.424000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30837,7 +30767,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>642.86400000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30861,7 +30791,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>137.28813559322035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30883,7 +30813,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>780.15213559322035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -30908,7 +30838,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>3.9007606779661019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -30918,7 +30848,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>784.05289627118646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -31450,20 +31380,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>4</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L16" s="118">
         <f>$I16*U16</f>
@@ -31471,19 +31399,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P16" s="118">
         <f>M16+N16+O16</f>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="318"/>
       <c r="S16" s="269">
@@ -31526,20 +31454,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>4</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L17" s="119">
         <f>$I17*U17</f>
@@ -31547,19 +31473,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="319"/>
       <c r="S17" s="269">
@@ -31604,20 +31530,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>2</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>104.925</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>8.3940000000000001</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>3.6723750000000002</v>
+        <v>0</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -31625,19 +31549,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>92.858624999999989</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>19.830508474576263</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>0.56344566737288126</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="5"/>
-        <v>113.25257914194913</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="319"/>
       <c r="S18" s="269">
@@ -32117,19 +32041,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>524.625</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>41.97</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>18.361875000000001</v>
+        <v>0</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -32137,19 +32061,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>464.29312499999992</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>99.152542372881314</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>2.8172283368644062</v>
+        <v>0</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>566.26289570974564</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -32203,7 +32127,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>524.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -32224,7 +32148,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>41.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -32245,7 +32169,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>18.361875000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -32267,7 +32191,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>464.29312499999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -32291,7 +32215,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>99.152542372881314</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -32313,7 +32237,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>563.4456673728813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -32338,7 +32262,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>2.8172283368644067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -32348,7 +32272,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>566.26289570974575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -33103,20 +33027,18 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>2</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>145.28</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>11.622400000000001</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>5.0848000000000004</v>
+        <v>0</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -33124,19 +33046,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>128.5728</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>27.457627118644069</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>0.78015213559322039</v>
+        <v>0</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="5"/>
-        <v>156.8105792542373</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="319"/>
       <c r="S19" s="269">
@@ -33177,20 +33099,18 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>4</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -33198,24 +33118,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="319"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>14.934340881355933</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -33256,20 +33176,18 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>4</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -33277,19 +33195,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="319"/>
       <c r="S21" s="269">
@@ -33547,19 +33465,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>726.40000000000009</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>58.112000000000009</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>25.423999999999999</v>
+        <v>0</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -33567,19 +33485,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>642.86400000000003</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>137.28813559322035</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>3.9007606779661019</v>
+        <v>0</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>784.05289627118646</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -33633,7 +33551,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>726.40000000000009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33654,7 +33572,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>58.112000000000009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33675,7 +33593,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>25.423999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33697,7 +33615,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>642.86400000000015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33721,7 +33639,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>137.28813559322035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33743,7 +33661,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>780.15213559322046</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -33768,7 +33686,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>3.9007606779661024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -33778,7 +33696,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>784.05289627118657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -34310,20 +34228,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>2</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>104.925</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>8.3940000000000001</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
-        <v>3.6723750000000002</v>
+        <v>0</v>
       </c>
       <c r="L16" s="118">
         <f>$I16*U16</f>
@@ -34331,19 +34247,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>92.858624999999989</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>19.830508474576263</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>0.56344566737288126</v>
+        <v>0</v>
       </c>
       <c r="P16" s="118">
         <f>M16+N16+O16</f>
-        <v>113.25257914194913</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="318"/>
       <c r="S16" s="269">
@@ -34386,20 +34302,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>4</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L17" s="119">
         <f>$I17*U17</f>
@@ -34407,19 +34321,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="319"/>
       <c r="S17" s="269">
@@ -34464,20 +34378,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>4</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -34485,19 +34397,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="5"/>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="319"/>
       <c r="S18" s="269">
@@ -34977,19 +34889,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>524.625</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>41.97</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>18.361875000000001</v>
+        <v>0</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -34997,19 +34909,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>464.29312499999997</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>99.152542372881314</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>2.8172283368644067</v>
+        <v>0</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>566.26289570974564</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -35063,7 +34975,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>524.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35084,7 +34996,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>41.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35105,7 +35017,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>18.361875000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35127,7 +35039,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>464.29312499999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35151,7 +35063,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>99.152542372881314</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35173,7 +35085,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>563.4456673728813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -35198,7 +35110,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>2.8172283368644067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -35208,7 +35120,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>566.26289570974575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -35963,20 +35875,18 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>4</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -35984,19 +35894,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="319"/>
       <c r="S19" s="269">
@@ -36037,20 +35947,18 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>2</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>145.28</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>11.622400000000001</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>5.0848000000000004</v>
+        <v>0</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -36058,24 +35966,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>128.5728</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>27.457627118644069</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>0.78015213559322039</v>
+        <v>0</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="5"/>
-        <v>156.8105792542373</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="319"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>7.4671704406779664</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -36116,20 +36024,18 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>4</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -36137,19 +36043,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="319"/>
       <c r="S21" s="269">
@@ -36407,19 +36313,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>726.40000000000009</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>58.112000000000009</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>25.423999999999999</v>
+        <v>0</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -36427,19 +36333,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>642.86400000000003</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>137.28813559322035</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>3.9007606779661019</v>
+        <v>0</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>784.05289627118646</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -36493,7 +36399,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>726.40000000000009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -36514,7 +36420,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>58.112000000000009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -36535,7 +36441,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>25.423999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -36557,7 +36463,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>642.86400000000015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -36581,7 +36487,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>137.28813559322035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -36603,7 +36509,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>780.15213559322046</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -36628,7 +36534,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>3.9007606779661024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -36638,7 +36544,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>784.05289627118657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -37170,20 +37076,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>4</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L16" s="118">
         <f>$I16*U16</f>
@@ -37191,19 +37095,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P16" s="118">
         <f>M16+N16+O16</f>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="318"/>
       <c r="S16" s="269">
@@ -37246,20 +37150,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>2</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>104.925</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>8.3940000000000001</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
-        <v>3.6723750000000002</v>
+        <v>0</v>
       </c>
       <c r="L17" s="119">
         <f>$I17*U17</f>
@@ -37267,19 +37169,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>92.858624999999989</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>19.830508474576263</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>0.56344566737288126</v>
+        <v>0</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>113.25257914194913</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="319"/>
       <c r="S17" s="269">
@@ -37324,20 +37226,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>4</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -37345,19 +37245,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="5"/>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="319"/>
       <c r="S18" s="269">
@@ -37837,19 +37737,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>524.625</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>41.97</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>18.361875000000001</v>
+        <v>0</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -37857,19 +37757,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>464.29312499999997</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>99.152542372881314</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>2.8172283368644067</v>
+        <v>0</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>566.26289570974564</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -37923,7 +37823,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>524.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -37944,7 +37844,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>41.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -37965,7 +37865,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>18.361875000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -37987,7 +37887,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>464.29312499999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -38011,7 +37911,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>99.152542372881314</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -38033,7 +37933,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>563.4456673728813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -38058,7 +37958,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>2.8172283368644067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -38068,7 +37968,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>566.26289570974575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -41596,20 +41496,18 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>4</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -41617,19 +41515,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="319"/>
       <c r="S19" s="269">
@@ -41670,20 +41568,18 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>4</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -41691,24 +41587,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="319"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>14.934340881355933</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -41749,20 +41645,18 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>2</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>145.28</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>11.622400000000001</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>5.0848000000000004</v>
+        <v>0</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -41770,19 +41664,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>128.5728</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>27.457627118644069</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>0.78015213559322039</v>
+        <v>0</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>156.8105792542373</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="319"/>
       <c r="S21" s="269">
@@ -42040,19 +41934,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>726.4</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>58.112000000000002</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>25.424000000000003</v>
+        <v>0</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -42060,19 +41954,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>642.86400000000003</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>137.28813559322035</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>3.9007606779661019</v>
+        <v>0</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>784.05289627118646</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -42126,7 +42020,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>726.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -42147,7 +42041,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>58.112000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -42168,7 +42062,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>25.424000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -42190,7 +42084,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>642.86400000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -42214,7 +42108,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>137.28813559322035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -42236,7 +42130,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>780.15213559322035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -42261,7 +42155,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>3.9007606779661019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -42271,7 +42165,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>784.05289627118646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -43026,20 +42920,18 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>2</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>145.28</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>11.622400000000001</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>5.0848000000000004</v>
+        <v>0</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -43047,19 +42939,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>128.5728</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>27.457627118644069</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>0.78015213559322039</v>
+        <v>0</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="5"/>
-        <v>156.8105792542373</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="319"/>
       <c r="S19" s="269">
@@ -43100,20 +42992,18 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>4</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -43121,24 +43011,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="319"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>14.934340881355933</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -43179,20 +43069,18 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>4</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -43200,19 +43088,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="319"/>
       <c r="S21" s="269">
@@ -43470,19 +43358,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>726.40000000000009</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>58.112000000000009</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>25.423999999999999</v>
+        <v>0</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -43490,19 +43378,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>642.86400000000003</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>137.28813559322035</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>3.9007606779661019</v>
+        <v>0</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>784.05289627118646</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -43556,7 +43444,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>726.40000000000009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -43577,7 +43465,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>58.112000000000009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -43598,7 +43486,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>25.423999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -43620,7 +43508,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>642.86400000000015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -43644,7 +43532,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>137.28813559322035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -43666,7 +43554,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>780.15213559322046</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -43691,7 +43579,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>3.9007606779661024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -43701,7 +43589,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>784.05289627118657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -54309,6 +54197,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:XEX51"/>
   <sheetFormatPr defaultColWidth="29.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -54527,7 +54418,7 @@
       </c>
       <c r="T6" s="301">
         <f>+'4'!P35</f>
-        <v>566.26289570974575</v>
+        <v>1132.5257914194915</v>
       </c>
       <c r="XEX6" t="s">
         <v>72</v>
@@ -54571,11 +54462,11 @@
       </c>
       <c r="J7" s="286">
         <f>+'1'!J16+'2'!J16+'3'!J16+'4'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16+'19'!J16+'20'!J16+'21'!J16+'22'!J16+'23'!J16+'24'!J16+'25'!J16+'26'!J16+'27'!J16+'28'!J16+'29'!J16+'30'!J16</f>
-        <v>230.83500000000006</v>
+        <v>230.83499999999998</v>
       </c>
       <c r="K7" s="286">
         <f>+'1'!K16+'2'!K16+'3'!K16+'4'!K16+'5'!K16+'6'!K16+'7'!K16+'8'!K16+'9'!K16+'10'!K16+'11'!K16+'12'!K16+'13'!K16+'14'!K16+'15'!K16+'16'!K16+'17'!K16+'18'!K16+'19'!K16+'20'!K16+'21'!K16+'22'!K16+'23'!K16+'24'!K16+'25'!K16+'26'!K16+'27'!K16+'28'!K16+'29'!K16+'30'!K16</f>
-        <v>100.99031250000003</v>
+        <v>100.99031250000002</v>
       </c>
       <c r="L7" s="286">
         <f>+'1'!L16+'2'!L16+'3'!L16+'4'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16+'11'!L16+'12'!L16+'13'!L16+'14'!L16+'15'!L16+'16'!L16+'17'!L16+'18'!L16+'19'!L16+'20'!L16+'21'!L16+'22'!L16+'23'!L16+'24'!L16+'25'!L16+'26'!L16+'27'!L16+'28'!L16+'29'!L16+'30'!L16</f>
@@ -54587,7 +54478,7 @@
       </c>
       <c r="N7" s="286">
         <f>+'1'!N16+'2'!N16+'3'!N16+'4'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16+'11'!N16+'12'!N16+'13'!N16+'14'!N16+'15'!N16+'16'!N16+'17'!N16+'18'!N16+'19'!N16+'20'!N16+'21'!N16+'22'!N16+'23'!N16+'24'!N16+'25'!N16+'26'!N16+'27'!N16+'28'!N16+'29'!N16+'30'!N16</f>
-        <v>545.33898305084745</v>
+        <v>545.33898305084722</v>
       </c>
       <c r="O7" s="286">
         <f>+'1'!O16+'2'!O16+'3'!O16+'4'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16+'11'!O16+'12'!O16+'13'!O16+'14'!O16+'15'!O16+'16'!O16+'17'!O16+'18'!O16+'19'!O16+'20'!O16+'21'!O16+'22'!O16+'23'!O16+'24'!O16+'25'!O16+'26'!O16+'27'!O16+'28'!O16+'29'!O16+'30'!O16</f>
@@ -54595,7 +54486,7 @@
       </c>
       <c r="P7" s="310">
         <f>M7+N7+O7</f>
-        <v>3114.4459264036018</v>
+        <v>3114.4459264036013</v>
       </c>
       <c r="Q7" s="213">
         <f>+'1'!Q16+'2'!Q16+'3'!Q16+'4'!Q16+'5'!Q16+'6'!Q16+'7'!Q16+'8'!Q16+'9'!Q16+'10'!Q16+'11'!Q16+'12'!Q16+'13'!Q16+'14'!Q16+'15'!Q16+'16'!Q16+'17'!Q16+'18'!Q16+'19'!Q16+'20'!Q16+'21'!Q16+'22'!Q16+'23'!Q16+'24'!Q16+'25'!Q16+'26'!Q16+'27'!Q16+'28'!Q16+'29'!Q16+'30'!Q16</f>
@@ -54610,7 +54501,7 @@
       </c>
       <c r="T7" s="301">
         <f>+'5'!P35</f>
-        <v>784.05289627118657</v>
+        <v>1132.5257914194915</v>
       </c>
       <c r="XEX7" t="s">
         <v>107</v>
@@ -54654,7 +54545,7 @@
       </c>
       <c r="J8" s="286">
         <f>+'1'!J17+'2'!J17+'3'!J17+'4'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17+'13'!J17+'14'!J17+'15'!J17+'16'!J17+'17'!J17+'18'!J17+'19'!J17+'20'!J17+'21'!J17+'22'!J17+'23'!J17+'24'!J17+'25'!J17+'26'!J17+'27'!J17+'28'!J17+'29'!J17+'30'!J17</f>
-        <v>209.85000000000005</v>
+        <v>209.85</v>
       </c>
       <c r="K8" s="286">
         <f>+'1'!K17+'2'!K17+'3'!K17+'4'!K17+'5'!K17+'6'!K17+'7'!K17+'8'!K17+'9'!K17+'10'!K17+'11'!K17+'12'!K17+'13'!K17+'14'!K17+'15'!K17+'16'!K17+'17'!K17+'18'!K17+'19'!K17+'20'!K17+'21'!K17+'22'!K17+'23'!K17+'24'!K17+'25'!K17+'26'!K17+'27'!K17+'28'!K17+'29'!K17+'30'!K17</f>
@@ -54670,11 +54561,11 @@
       </c>
       <c r="N8" s="286">
         <f>+'1'!N17+'2'!N17+'3'!N17+'4'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17+'11'!N17+'12'!N17+'13'!N17+'14'!N17+'15'!N17+'16'!N17+'17'!N17+'18'!N17+'19'!N17+'20'!N17+'21'!N17+'22'!N17+'23'!N17+'24'!N17+'25'!N17+'26'!N17+'27'!N17+'28'!N17+'29'!N17+'30'!N17</f>
-        <v>495.7627118644067</v>
+        <v>495.76271186440658</v>
       </c>
       <c r="O8" s="286">
         <f>+'1'!O17+'2'!O17+'3'!O17+'4'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17+'11'!O17+'12'!O17+'13'!O17+'14'!O17+'15'!O17+'16'!O17+'17'!O17+'18'!O17+'19'!O17+'20'!O17+'21'!O17+'22'!O17+'23'!O17+'24'!O17+'25'!O17+'26'!O17+'27'!O17+'28'!O17+'29'!O17+'30'!O17</f>
-        <v>14.086141684322032</v>
+        <v>14.086141684322033</v>
       </c>
       <c r="P8" s="311">
         <f t="shared" ref="P8:P15" si="2">M8+N8+O8</f>
@@ -54693,7 +54584,7 @@
       </c>
       <c r="T8" s="301">
         <f>+'6'!P35</f>
-        <v>566.26289570974575</v>
+        <v>1132.5257914194915</v>
       </c>
       <c r="XEX8" t="s">
         <v>108</v>
@@ -54737,11 +54628,11 @@
       </c>
       <c r="J9" s="286">
         <f>+'1'!J18+'2'!J18+'3'!J18+'4'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18+'19'!J18+'20'!J18+'21'!J18+'22'!J18+'23'!J18+'24'!J18+'25'!J18+'26'!J18+'27'!J18+'28'!J18+'29'!J18+'30'!J18</f>
-        <v>398.71500000000009</v>
+        <v>398.71499999999997</v>
       </c>
       <c r="K9" s="286">
         <f>+'1'!K18+'2'!K18+'3'!K18+'4'!K18+'5'!K18+'6'!K18+'7'!K18+'8'!K18+'9'!K18+'10'!K18+'11'!K18+'12'!K18+'13'!K18+'14'!K18+'15'!K18+'16'!K18+'17'!K18+'18'!K18+'19'!K18+'20'!K18+'21'!K18+'22'!K18+'23'!K18+'24'!K18+'25'!K18+'26'!K18+'27'!K18+'28'!K18+'29'!K18+'30'!K18</f>
-        <v>174.43781250000004</v>
+        <v>174.43781250000001</v>
       </c>
       <c r="L9" s="286">
         <f>+'1'!L18+'2'!L18+'3'!L18+'4'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18+'11'!L18+'12'!L18+'13'!L18+'14'!L18+'15'!L18+'16'!L18+'17'!L18+'18'!L18+'19'!L18+'20'!L18+'21'!L18+'22'!L18+'23'!L18+'24'!L18+'25'!L18+'26'!L18+'27'!L18+'28'!L18+'29'!L18+'30'!L18</f>
@@ -54753,11 +54644,11 @@
       </c>
       <c r="N9" s="286">
         <f>+'1'!N18+'2'!N18+'3'!N18+'4'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18+'11'!N18+'12'!N18+'13'!N18+'14'!N18+'15'!N18+'16'!N18+'17'!N18+'18'!N18+'19'!N18+'20'!N18+'21'!N18+'22'!N18+'23'!N18+'24'!N18+'25'!N18+'26'!N18+'27'!N18+'28'!N18+'29'!N18+'30'!N18</f>
-        <v>941.94915254237276</v>
+        <v>941.94915254237253</v>
       </c>
       <c r="O9" s="286">
         <f>+'1'!O18+'2'!O18+'3'!O18+'4'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18+'11'!O18+'12'!O18+'13'!O18+'14'!O18+'15'!O18+'16'!O18+'17'!O18+'18'!O18+'19'!O18+'20'!O18+'21'!O18+'22'!O18+'23'!O18+'24'!O18+'25'!O18+'26'!O18+'27'!O18+'28'!O18+'29'!O18+'30'!O18</f>
-        <v>26.763669200211876</v>
+        <v>26.763669200211865</v>
       </c>
       <c r="P9" s="311">
         <f t="shared" si="2"/>
@@ -54776,7 +54667,7 @@
       </c>
       <c r="T9" s="301">
         <f>+'7'!P35</f>
-        <v>784.05289627118657</v>
+        <v>1132.5257914194915</v>
       </c>
     </row>
     <row r="10" spans="1:20 16377:16378" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -54817,7 +54708,7 @@
       </c>
       <c r="J10" s="286">
         <f>+'1'!J19+'2'!J19+'3'!J19+'4'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19+'19'!J19+'20'!J19+'21'!J19+'22'!J19+'23'!J19+'24'!J19+'25'!J19+'26'!J19+'27'!J19+'28'!J19+'29'!J19+'30'!J19</f>
-        <v>552.06400000000008</v>
+        <v>552.06399999999996</v>
       </c>
       <c r="K10" s="286">
         <f>+'1'!K19+'2'!K19+'3'!K19+'4'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19+'11'!K19+'12'!K19+'13'!K19+'14'!K19+'15'!K19+'16'!K19+'17'!K19+'18'!K19+'19'!K19+'20'!K19+'21'!K19+'22'!K19+'23'!K19+'24'!K19+'25'!K19+'26'!K19+'27'!K19+'28'!K19+'29'!K19+'30'!K19</f>
@@ -54833,11 +54724,11 @@
       </c>
       <c r="N10" s="286">
         <f>+'1'!N19+'2'!N19+'3'!N19+'4'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19+'11'!N19+'12'!N19+'13'!N19+'14'!N19+'15'!N19+'16'!N19+'17'!N19+'18'!N19+'19'!N19+'20'!N19+'21'!N19+'22'!N19+'23'!N19+'24'!N19+'25'!N19+'26'!N19+'27'!N19+'28'!N19+'29'!N19+'30'!N19</f>
-        <v>1304.2372881355927</v>
+        <v>1304.2372881355932</v>
       </c>
       <c r="O10" s="286">
         <f>+'1'!O19+'2'!O19+'3'!O19+'4'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19+'11'!O19+'12'!O19+'13'!O19+'14'!O19+'15'!O19+'16'!O19+'17'!O19+'18'!O19+'19'!O19+'20'!O19+'21'!O19+'22'!O19+'23'!O19+'24'!O19+'25'!O19+'26'!O19+'27'!O19+'28'!O19+'29'!O19+'30'!O19</f>
-        <v>37.057226440677951</v>
+        <v>37.057226440677965</v>
       </c>
       <c r="P10" s="311">
         <f t="shared" si="2"/>
@@ -54856,7 +54747,7 @@
       </c>
       <c r="T10" s="301">
         <f>+'8'!P35</f>
-        <v>566.26289570974575</v>
+        <v>1132.5257914194915</v>
       </c>
     </row>
     <row r="11" spans="1:20 16377:16378" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -54901,7 +54792,7 @@
       </c>
       <c r="K11" s="286">
         <f>+'1'!K20+'2'!K20+'3'!K20+'4'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20+'11'!K20+'12'!K20+'13'!K20+'14'!K20+'15'!K20+'16'!K20+'17'!K20+'18'!K20+'19'!K20+'20'!K20+'21'!K20+'22'!K20+'23'!K20+'24'!K20+'25'!K20+'26'!K20+'27'!K20+'28'!K20+'29'!K20+'30'!K20</f>
-        <v>127.12000000000002</v>
+        <v>127.12</v>
       </c>
       <c r="L11" s="286">
         <f>+'1'!L20+'2'!L20+'3'!L20+'4'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20+'11'!L20+'12'!L20+'13'!L20+'14'!L20+'15'!L20+'16'!L20+'17'!L20+'18'!L20+'19'!L20+'20'!L20+'21'!L20+'22'!L20+'23'!L20+'24'!L20+'25'!L20+'26'!L20+'27'!L20+'28'!L20+'29'!L20+'30'!L20</f>
@@ -54936,7 +54827,7 @@
       </c>
       <c r="T11" s="301">
         <f>+'9'!P35</f>
-        <v>784.05289627118657</v>
+        <v>1132.5257914194915</v>
       </c>
     </row>
     <row r="12" spans="1:20 16377:16378" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -54977,7 +54868,7 @@
       </c>
       <c r="J12" s="286">
         <f>+'1'!J21+'2'!J21+'3'!J21+'4'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21+'19'!J21+'20'!J21+'21'!J21+'22'!J21+'23'!J21+'24'!J21+'25'!J21+'26'!J21+'27'!J21+'28'!J21+'29'!J21+'30'!J21</f>
-        <v>319.61600000000004</v>
+        <v>319.61599999999999</v>
       </c>
       <c r="K12" s="286">
         <f>+'1'!K21+'2'!K21+'3'!K21+'4'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21+'11'!K21+'12'!K21+'13'!K21+'14'!K21+'15'!K21+'16'!K21+'17'!K21+'18'!K21+'19'!K21+'20'!K21+'21'!K21+'22'!K21+'23'!K21+'24'!K21+'25'!K21+'26'!K21+'27'!K21+'28'!K21+'29'!K21+'30'!K21</f>
@@ -54989,19 +54880,19 @@
       </c>
       <c r="M12" s="230">
         <f t="shared" si="1"/>
-        <v>3535.7519999999995</v>
+        <v>3535.752</v>
       </c>
       <c r="N12" s="286">
         <f>+'1'!N21+'2'!N21+'3'!N21+'4'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21+'11'!N21+'12'!N21+'13'!N21+'14'!N21+'15'!N21+'16'!N21+'17'!N21+'18'!N21+'19'!N21+'20'!N21+'21'!N21+'22'!N21+'23'!N21+'24'!N21+'25'!N21+'26'!N21+'27'!N21+'28'!N21+'29'!N21+'30'!N21</f>
-        <v>755.08474576271169</v>
+        <v>755.08474576271192</v>
       </c>
       <c r="O12" s="286">
         <f>+'1'!O21+'2'!O21+'3'!O21+'4'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21+'11'!O21+'12'!O21+'13'!O21+'14'!O21+'15'!O21+'16'!O21+'17'!O21+'18'!O21+'19'!O21+'20'!O21+'21'!O21+'22'!O21+'23'!O21+'24'!O21+'25'!O21+'26'!O21+'27'!O21+'28'!O21+'29'!O21+'30'!O21</f>
-        <v>21.454183728813554</v>
+        <v>21.454183728813561</v>
       </c>
       <c r="P12" s="311">
         <f t="shared" si="2"/>
-        <v>4312.2909294915244</v>
+        <v>4312.2909294915253</v>
       </c>
       <c r="Q12" s="213">
         <f>+'1'!Q21+'2'!Q21+'3'!Q21+'4'!Q21+'5'!Q21+'6'!Q21+'7'!Q21+'8'!Q21+'9'!Q21+'10'!Q21+'11'!Q21+'12'!Q21+'13'!Q21+'14'!Q21+'15'!Q21+'16'!Q21+'17'!Q21+'18'!Q21+'19'!Q21+'20'!Q21+'21'!Q21+'22'!Q21+'23'!Q21+'24'!Q21+'25'!Q21+'26'!Q21+'27'!Q21+'28'!Q21+'29'!Q21+'30'!Q21</f>
@@ -55016,7 +54907,7 @@
       </c>
       <c r="T12" s="301">
         <f>+'10'!P35</f>
-        <v>566.26289570974575</v>
+        <v>1568.1057925423729</v>
       </c>
     </row>
     <row r="13" spans="1:20 16377:16378" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55096,7 +54987,7 @@
       </c>
       <c r="T13" s="301">
         <f>+'11'!P35</f>
-        <v>566.26289570974575</v>
+        <v>1568.1057925423729</v>
       </c>
     </row>
     <row r="14" spans="1:20 16377:16378" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55176,7 +55067,7 @@
       </c>
       <c r="T14" s="301">
         <f>+'12'!P35</f>
-        <v>784.05289627118646</v>
+        <v>1568.1057925423729</v>
       </c>
     </row>
     <row r="15" spans="1:20 16377:16378" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -55256,7 +55147,7 @@
       </c>
       <c r="T15" s="301">
         <f>+'13'!P35</f>
-        <v>566.26289570974575</v>
+        <v>1568.1057925423729</v>
       </c>
     </row>
     <row r="16" spans="1:20 16377:16378" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -55285,7 +55176,7 @@
       </c>
       <c r="J16" s="274">
         <f>SUM(J7:J15)</f>
-        <v>2001.6400000000003</v>
+        <v>2001.6399999999999</v>
       </c>
       <c r="K16" s="275">
         <f t="shared" si="3"/>
@@ -55309,7 +55200,7 @@
       </c>
       <c r="P16" s="113">
         <f>SUM(P7:P15)</f>
-        <v>27006.315839618641</v>
+        <v>27006.315839618645</v>
       </c>
       <c r="Q16" s="128">
         <f>SUM(Q7:Q15)</f>
@@ -55324,7 +55215,7 @@
       </c>
       <c r="T16" s="301">
         <f>+'14'!P35</f>
-        <v>784.05289627118646</v>
+        <v>1568.1057925423729</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55352,7 +55243,7 @@
       </c>
       <c r="T17" s="301">
         <f>+'15'!P35</f>
-        <v>566.26289570974575</v>
+        <v>1568.1057925423729</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -55373,7 +55264,7 @@
       </c>
       <c r="T18" s="301">
         <f>+'16'!P35</f>
-        <v>784.05289627118657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55407,7 +55298,7 @@
       </c>
       <c r="T19" s="301">
         <f>+'17'!P35</f>
-        <v>566.26289570974575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55428,7 +55319,7 @@
       <c r="O20" s="371"/>
       <c r="P20" s="140">
         <f>+J16</f>
-        <v>2001.6400000000003</v>
+        <v>2001.6399999999999</v>
       </c>
       <c r="R20" s="299">
         <v>18</v>
@@ -55439,7 +55330,7 @@
       </c>
       <c r="T20" s="301">
         <f>+'18'!P35</f>
-        <v>784.05289627118657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55471,7 +55362,7 @@
       </c>
       <c r="T21" s="301">
         <f>+'19'!P35</f>
-        <v>566.26289570974575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55504,7 +55395,7 @@
       </c>
       <c r="T22" s="301">
         <f>+'20'!P35</f>
-        <v>784.05289627118646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55539,7 +55430,7 @@
       </c>
       <c r="T23" s="301">
         <f>+'21'!P35</f>
-        <v>566.26289570974575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55572,7 +55463,7 @@
       </c>
       <c r="T24" s="301">
         <f>+'22'!P35</f>
-        <v>784.05289627118657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -55608,7 +55499,7 @@
       </c>
       <c r="T25" s="301">
         <f>+'23'!P35</f>
-        <v>566.26289570974575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -55629,7 +55520,7 @@
       </c>
       <c r="T26" s="301">
         <f>+'24'!P35</f>
-        <v>784.05289627118657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -55654,7 +55545,7 @@
       </c>
       <c r="T27" s="301">
         <f>+'25'!P35</f>
-        <v>566.26289570974575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55667,7 +55558,7 @@
       </c>
       <c r="T28" s="301">
         <f>+'26'!P35</f>
-        <v>784.05289627118646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55683,7 +55574,7 @@
       </c>
       <c r="T29" s="301">
         <f>+'27'!P35</f>
-        <v>784.05289627118657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55732,7 +55623,7 @@
       </c>
       <c r="T33" s="304">
         <f>SUM(T3:T32)</f>
-        <v>27006.315839618637</v>
+        <v>27006.315839618652</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.35">
@@ -55808,7 +55699,7 @@
     <mergeCell ref="I5:I6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -60518,20 +60409,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>4</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>209.85</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>16.788</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
-        <v>7.3447500000000003</v>
+        <v>0</v>
       </c>
       <c r="L16" s="118">
         <f>$I16*U16</f>
@@ -60539,19 +60428,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>185.71724999999998</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>39.661016949152526</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>1.1268913347457625</v>
+        <v>0</v>
       </c>
       <c r="P16" s="118">
         <f>M16+N16+O16</f>
-        <v>226.50515828389825</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="318"/>
       <c r="S16" s="269">
@@ -60594,20 +60483,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>2</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>104.925</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>8.3940000000000001</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
-        <v>3.6723750000000002</v>
+        <v>0</v>
       </c>
       <c r="L17" s="119">
         <f>$I17*U17</f>
@@ -60615,19 +60502,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>92.858624999999989</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>19.830508474576263</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>0.56344566737288126</v>
+        <v>0</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>113.25257914194913</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="319"/>
       <c r="S17" s="269">
@@ -60673,19 +60560,19 @@
       </c>
       <c r="G18" s="287"/>
       <c r="H18" s="96">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>209.85</v>
+        <v>1049.25</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>16.788</v>
+        <v>83.94</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>7.3447500000000003</v>
+        <v>36.723750000000003</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -60693,19 +60580,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>185.71724999999998</v>
+        <v>928.58625000000006</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>39.661016949152526</v>
+        <v>198.30508474576263</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>1.1268913347457625</v>
+        <v>5.6344566737288133</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="5"/>
-        <v>226.50515828389825</v>
+        <v>1132.5257914194915</v>
       </c>
       <c r="Q18" s="319"/>
       <c r="S18" s="269">
@@ -61185,19 +61072,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>524.625</v>
+        <v>1049.25</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>41.97</v>
+        <v>83.94</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>18.361875000000001</v>
+        <v>36.723750000000003</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -61205,19 +61092,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>464.29312499999997</v>
+        <v>928.58625000000006</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>99.152542372881314</v>
+        <v>198.30508474576263</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>2.8172283368644067</v>
+        <v>5.6344566737288133</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>566.26289570974564</v>
+        <v>1132.5257914194915</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -61271,7 +61158,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>524.625</v>
+        <v>1049.25</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -61292,7 +61179,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>41.97</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -61313,7 +61200,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>18.361875000000001</v>
+        <v>36.723750000000003</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -61335,7 +61222,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>464.29312499999997</v>
+        <v>928.58624999999995</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -61359,7 +61246,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>99.152542372881314</v>
+        <v>198.30508474576263</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -61381,7 +61268,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>563.4456673728813</v>
+        <v>1126.8913347457626</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -61406,7 +61293,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>2.8172283368644067</v>
+        <v>5.6344566737288133</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -61416,7 +61303,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>566.26289570974575</v>
+        <v>1132.5257914194915</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -62098,18 +61985,20 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96"/>
+      <c r="H18" s="96">
+        <v>20</v>
+      </c>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1049.25</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>83.94</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>36.723750000000003</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -62117,19 +62006,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>928.58625000000006</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>198.30508474576263</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5.6344566737288133</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1132.5257914194915</v>
       </c>
       <c r="Q18" s="319"/>
       <c r="S18" s="269">
@@ -62171,20 +62060,18 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>4</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -62192,19 +62079,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="319"/>
       <c r="S19" s="269">
@@ -62245,20 +62132,18 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>2</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>145.28</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>11.622400000000001</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>5.0848000000000004</v>
+        <v>0</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -62266,19 +62151,19 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>128.5728</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>27.457627118644069</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>0.78015213559322039</v>
+        <v>0</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="5"/>
-        <v>156.8105792542373</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="319"/>
       <c r="S20" s="269">
@@ -62320,20 +62205,18 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>4</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>290.56</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>23.244800000000001</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>10.169600000000001</v>
+        <v>0</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -62341,19 +62224,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>257.1456</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>54.915254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>1.5603042711864408</v>
+        <v>0</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>313.62115850847459</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="319"/>
       <c r="S21" s="269">
@@ -62611,19 +62494,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>726.40000000000009</v>
+        <v>1049.25</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>58.112000000000009</v>
+        <v>83.94</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>25.423999999999999</v>
+        <v>36.723750000000003</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -62631,19 +62514,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>642.86400000000003</v>
+        <v>928.58625000000006</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>137.28813559322035</v>
+        <v>198.30508474576263</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>3.9007606779661019</v>
+        <v>5.6344566737288133</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>784.05289627118646</v>
+        <v>1132.5257914194915</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -62697,7 +62580,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>726.40000000000009</v>
+        <v>1049.25</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -62718,7 +62601,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>58.112000000000009</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -62739,7 +62622,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>25.423999999999999</v>
+        <v>36.723750000000003</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -62761,7 +62644,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>642.86400000000015</v>
+        <v>928.58624999999995</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -62785,7 +62668,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>137.28813559322035</v>
+        <v>198.30508474576263</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -62807,7 +62690,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>780.15213559322046</v>
+        <v>1126.8913347457626</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -62832,7 +62715,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>3.9007606779661024</v>
+        <v>5.6344566737288133</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -62842,7 +62725,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>784.05289627118657</v>
+        <v>1132.5257914194915</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
